--- a/assets/constructions/examples/ctd_mha1.xlsx
+++ b/assets/constructions/examples/ctd_mha1.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ctd" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="ctd" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC6"/>
+  <dimension ref="A1:AH6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -574,11 +574,36 @@
           <t>kwy</t>
         </is>
       </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>lcs</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>pricecurrency</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue_rub</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>316-12CM600-12015G  1030</t>
+          <t>A316-16CM800-06249G 1030</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -588,7 +613,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>CoroMill®316..CM..G</t>
+          <t>CoroMill® 316..CM..G</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -601,17 +626,17 @@
         <v>3</v>
       </c>
       <c r="G2" t="n">
-        <v>12</v>
+        <v>15.875</v>
       </c>
       <c r="H2" t="n">
-        <v>1.2</v>
+        <v>7.4</v>
       </c>
       <c r="I2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>METRIC_EH:12</t>
+          <t>INCH_EH:16</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -643,26 +668,26 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>11.7</v>
+        <v>15.5</v>
       </c>
       <c r="R2" t="n">
-        <v>14.5</v>
+        <v>18.7</v>
       </c>
       <c r="S2" t="n">
-        <v>11.7</v>
+        <v>15.5</v>
       </c>
       <c r="T2" t="n">
         <v>80000</v>
       </c>
       <c r="U2" t="n">
-        <v>0.038</v>
+        <v>0.075</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>9,1</t>
+          <t>10,2</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -671,7 +696,7 @@
         </is>
       </c>
       <c r="Y2" t="n">
-        <v>15</v>
+        <v>49</v>
       </c>
       <c r="Z2" t="inlineStr"/>
       <c r="AA2" t="b">
@@ -679,44 +704,55 @@
       </c>
       <c r="AB2" t="inlineStr"/>
       <c r="AC2" t="inlineStr"/>
+      <c r="AD2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE2" t="inlineStr"/>
+      <c r="AF2" t="inlineStr"/>
+      <c r="AG2" t="inlineStr"/>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>PMKS</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A316-10CM400-03730G 1030</t>
+          <t>MM ECF120-02/120-4T08 IC908</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>SANDVIK</t>
+          <t>ISCAR</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>CoroMill® 316..CM..G</t>
+          <t>MM ECF</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>PMKS</t>
+          <t>PMKSH</t>
         </is>
       </c>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G3" t="n">
-        <v>9.525</v>
+        <v>12</v>
       </c>
       <c r="H3" t="n">
-        <v>1.85</v>
+        <v>2.9</v>
       </c>
       <c r="I3" t="n">
         <v>4</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>INCH_EH:10</t>
+          <t>ISCAR_MM:T08</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -726,48 +762,34 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>1030</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>HC</t>
-        </is>
-      </c>
+          <t>IC908</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
-          <t>PVD(Ti,Al)</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>COROMANT</t>
-        </is>
-      </c>
+          <t>TiAlN</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr"/>
       <c r="P3" t="n">
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>9.25</v>
+        <v>12</v>
       </c>
       <c r="R3" t="n">
-        <v>12.4</v>
-      </c>
-      <c r="S3" t="n">
-        <v>9.25</v>
-      </c>
-      <c r="T3" t="n">
-        <v>80000</v>
-      </c>
-      <c r="U3" t="n">
-        <v>0.025</v>
-      </c>
+        <v>16.5</v>
+      </c>
+      <c r="S3" t="inlineStr"/>
+      <c r="T3" t="inlineStr"/>
+      <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
         <v>0</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>9,1</t>
+          <t>2013/Multi_Master_Catalog.pdf</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -784,44 +806,55 @@
       </c>
       <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="inlineStr"/>
+      <c r="AD3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE3" t="inlineStr"/>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="inlineStr"/>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>PMKSH</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>MM HCD.750-080-2T12 IC908</t>
+          <t>A316-12CM600-05045G 1030</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ISCAR</t>
+          <t>SANDVIK</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>MM HCD</t>
+          <t>CoroMill® 316..CM..G</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>PMKSH</t>
+          <t>PMKS</t>
         </is>
       </c>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G4" t="n">
-        <v>19</v>
+        <v>12.7</v>
       </c>
       <c r="H4" t="n">
-        <v>11</v>
+        <v>4.85</v>
       </c>
       <c r="I4" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>ISCAR_MM:T12</t>
+          <t>INCH_EH:12</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -831,34 +864,48 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>IC908</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr"/>
+          <t>1030</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>HC</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>TiAlN</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr"/>
+          <t>PVD(Ti,Al)</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>COROMANT</t>
+        </is>
+      </c>
       <c r="P4" t="n">
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>18.3</v>
+        <v>12.3</v>
       </c>
       <c r="R4" t="n">
-        <v>24.7</v>
-      </c>
-      <c r="S4" t="inlineStr"/>
-      <c r="T4" t="inlineStr"/>
-      <c r="U4" t="inlineStr"/>
+        <v>13</v>
+      </c>
+      <c r="S4" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="T4" t="n">
+        <v>80000</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0.035</v>
+      </c>
       <c r="V4" t="n">
         <v>0</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>2013/Multi_Master_Catalog.pdf</t>
+          <t>9,1</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -867,7 +914,7 @@
         </is>
       </c>
       <c r="Y4" t="n">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="Z4" t="inlineStr"/>
       <c r="AA4" t="b">
@@ -875,44 +922,55 @@
       </c>
       <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="inlineStr"/>
+      <c r="AD4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE4" t="inlineStr"/>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="inlineStr"/>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>PMKS</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>MM HCD104-090-2T06 IC908</t>
+          <t>A316-16CM800-06260G 1030</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ISCAR</t>
+          <t>SANDVIK</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>MM HCD</t>
+          <t>CoroMill® 316..CM..G</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>PMKSH</t>
+          <t>PMKS</t>
         </is>
       </c>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="n">
-        <v>1.5</v>
+        <v>7</v>
       </c>
       <c r="G5" t="n">
-        <v>10.4</v>
+        <v>15.875</v>
       </c>
       <c r="H5" t="n">
-        <v>4.6</v>
+        <v>7.7</v>
       </c>
       <c r="I5" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>ISCAR_MM:T06</t>
+          <t>INCH_EH:16</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -922,34 +980,48 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>IC908</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr"/>
+          <t>1030</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>HC</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>TiAlN</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr"/>
+          <t>PVD(Ti,Al)</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>COROMANT</t>
+        </is>
+      </c>
       <c r="P5" t="n">
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>9.6</v>
+        <v>15.5</v>
       </c>
       <c r="R5" t="n">
-        <v>11.75</v>
-      </c>
-      <c r="S5" t="inlineStr"/>
-      <c r="T5" t="inlineStr"/>
-      <c r="U5" t="inlineStr"/>
+        <v>18.7</v>
+      </c>
+      <c r="S5" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="T5" t="n">
+        <v>80000</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0.062</v>
+      </c>
       <c r="V5" t="n">
         <v>0</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>2013/Multi_Master_Catalog.pdf</t>
+          <t>9,1</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -958,7 +1030,7 @@
         </is>
       </c>
       <c r="Y5" t="n">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="Z5" t="inlineStr"/>
       <c r="AA5" t="b">
@@ -966,44 +1038,55 @@
       </c>
       <c r="AB5" t="inlineStr"/>
       <c r="AC5" t="inlineStr"/>
+      <c r="AD5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE5" t="inlineStr"/>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="inlineStr"/>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>PMKS</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A316-12CM600-05060G 1030</t>
+          <t>MM ECF60-02/100-4T06 IC908</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>SANDVIK</t>
+          <t>ISCAR</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>CoroMill® 316..CM..G</t>
+          <t>MM ECF</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>PMKS</t>
+          <t>PMKSH</t>
         </is>
       </c>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="n">
-        <v>4.5</v>
+        <v>2</v>
       </c>
       <c r="G6" t="n">
-        <v>12.7</v>
+        <v>10</v>
       </c>
       <c r="H6" t="n">
-        <v>7.1</v>
+        <v>6.9</v>
       </c>
       <c r="I6" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>INCH_EH:12</t>
+          <t>ISCAR_MM:T06</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1013,48 +1096,34 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>1030</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>HC</t>
-        </is>
-      </c>
+          <t>IC908</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
-          <t>PVD(Ti,Al)</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>COROMANT</t>
-        </is>
-      </c>
+          <t>TiAlN</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr"/>
       <c r="P6" t="n">
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>12.3</v>
+        <v>10</v>
       </c>
       <c r="R6" t="n">
-        <v>14.6</v>
-      </c>
-      <c r="S6" t="n">
-        <v>12.3</v>
-      </c>
-      <c r="T6" t="n">
-        <v>80000</v>
-      </c>
-      <c r="U6" t="n">
-        <v>0.034</v>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="S6" t="inlineStr"/>
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
         <v>0</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>9,1</t>
+          <t>2013/Multi_Master_Catalog.pdf</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1071,6 +1140,17 @@
       </c>
       <c r="AB6" t="inlineStr"/>
       <c r="AC6" t="inlineStr"/>
+      <c r="AD6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE6" t="inlineStr"/>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="inlineStr"/>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>PMKSH</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
